--- a/.agents/skills/proto/assets/Adventure_template/split_xlsx/quest.xlsx
+++ b/.agents/skills/proto/assets/Adventure_template/split_xlsx/quest.xlsx
@@ -899,9 +899,9 @@
     <col width="63.5703125" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="17.28515625" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="92.7109375" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="21.42578125" customWidth="1" min="12" max="12"/>
@@ -1004,8 +1004,16 @@
           <t>int</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
@@ -1052,8 +1060,16 @@
           <t>id</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>tasks.0.identifier</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
@@ -1117,8 +1133,16 @@
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="1" t="n"/>
       <c r="D6" s="1" t="n"/>
-      <c r="E6" s="1" t="n"/>
-      <c r="F6" s="1" t="n"/>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Adventure_GR_3</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Adventure_GR_3</t>
+        </is>
+      </c>
       <c r="G6" s="1" t="n"/>
       <c r="H6" s="1" t="n"/>
       <c r="I6" s="1" t="n"/>
@@ -1454,7 +1478,11 @@
           <t>string</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n"/>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
@@ -1506,7 +1534,11 @@
           <t>tasks.0.identifier</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n"/>
+      <c r="J19" s="1" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
       <c r="M19" s="4" t="n"/>
@@ -1740,7 +1772,11 @@
           <t>string</t>
         </is>
       </c>
-      <c r="H27" s="4" t="n"/>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="I27" s="4" t="n"/>
       <c r="J27" s="4" t="n"/>
       <c r="K27" s="4" t="n"/>
@@ -1788,7 +1824,11 @@
           <t>tasks.0.identifier</t>
         </is>
       </c>
-      <c r="H28" s="4" t="n"/>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
@@ -2036,7 +2076,11 @@
           <t>string</t>
         </is>
       </c>
-      <c r="J36" s="4" t="n"/>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="K36" s="4" t="n"/>
       <c r="L36" s="4" t="n"/>
       <c r="M36" s="4" t="n"/>
@@ -2092,7 +2136,11 @@
           <t>tasks.0.identifier</t>
         </is>
       </c>
-      <c r="J37" s="4" t="n"/>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="K37" s="4" t="n"/>
       <c r="L37" s="4" t="n"/>
       <c r="M37" s="4" t="n"/>
@@ -2341,7 +2389,11 @@
           <t>string</t>
         </is>
       </c>
-      <c r="H45" s="4" t="n"/>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="I45" s="4" t="n"/>
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
@@ -2390,7 +2442,11 @@
           <t>tasks.0.identifier</t>
         </is>
       </c>
-      <c r="H46" s="4" t="n"/>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="I46" s="4" t="n"/>
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
@@ -2640,7 +2696,11 @@
           <t>string</t>
         </is>
       </c>
-      <c r="J54" s="4" t="n"/>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="K54" s="4" t="n"/>
       <c r="L54" s="4" t="n"/>
       <c r="M54" s="4" t="n"/>
@@ -2696,7 +2756,11 @@
           <t>tasks.0.identifier</t>
         </is>
       </c>
-      <c r="J55" s="4" t="n"/>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
       <c r="M55" s="4" t="n"/>
@@ -2944,7 +3008,11 @@
           <t>string</t>
         </is>
       </c>
-      <c r="H63" s="4" t="n"/>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="I63" s="4" t="n"/>
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="4" t="n"/>
@@ -2993,7 +3061,11 @@
           <t>tasks.0.identifier</t>
         </is>
       </c>
-      <c r="H64" s="4" t="n"/>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="I64" s="4" t="n"/>
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="4" t="n"/>
@@ -3232,8 +3304,16 @@
           <t>int</t>
         </is>
       </c>
-      <c r="G72" s="4" t="n"/>
-      <c r="H72" s="4" t="n"/>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="I72" s="4" t="n"/>
       <c r="J72" s="4" t="n"/>
       <c r="K72" s="4" t="n"/>
@@ -3277,8 +3357,16 @@
           <t>id</t>
         </is>
       </c>
-      <c r="G73" s="4" t="n"/>
-      <c r="H73" s="4" t="n"/>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>tasks.0.identifier</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="I73" s="4" t="n"/>
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
@@ -3492,8 +3580,16 @@
           <t>int</t>
         </is>
       </c>
-      <c r="G80" s="4" t="n"/>
-      <c r="H80" s="4" t="n"/>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="I80" s="4" t="n"/>
       <c r="J80" s="4" t="n"/>
       <c r="K80" s="4" t="n"/>
@@ -3536,8 +3632,16 @@
           <t>id</t>
         </is>
       </c>
-      <c r="G81" s="4" t="n"/>
-      <c r="H81" s="4" t="n"/>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>tasks.0.identifier</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>tasks.0.title</t>
+        </is>
+      </c>
       <c r="I81" s="4" t="n"/>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
